--- a/artfynd/A 2708-2020 artfynd.xlsx
+++ b/artfynd/A 2708-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 2708-2020 artfynd.xlsx
+++ b/artfynd/A 2708-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -797,6 +797,122 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>122485464</v>
+      </c>
+      <c r="B3" t="n">
+        <v>90853</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Sylbergen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>558140</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6633143</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Äldre tallskog, lav-ristyp</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Äldre tall</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Aivars Dunskis</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2708-2020 artfynd.xlsx
+++ b/artfynd/A 2708-2020 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>122485464</v>
       </c>
       <c r="B3" t="n">
-        <v>90853</v>
+        <v>90854</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 2708-2020 artfynd.xlsx
+++ b/artfynd/A 2708-2020 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>122485464</v>
       </c>
       <c r="B3" t="n">
-        <v>90854</v>
+        <v>90857</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 2708-2020 artfynd.xlsx
+++ b/artfynd/A 2708-2020 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>122485464</v>
       </c>
       <c r="B3" t="n">
-        <v>90857</v>
+        <v>90960</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 2708-2020 artfynd.xlsx
+++ b/artfynd/A 2708-2020 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>122485464</v>
       </c>
       <c r="B3" t="n">
-        <v>90960</v>
+        <v>90964</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 2708-2020 artfynd.xlsx
+++ b/artfynd/A 2708-2020 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>122485464</v>
       </c>
       <c r="B3" t="n">
-        <v>90964</v>
+        <v>90972</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 2708-2020 artfynd.xlsx
+++ b/artfynd/A 2708-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,6 +914,127 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123404102</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57497</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Sylbergen, Sylbergen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>558318</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6633047</v>
+      </c>
+      <c r="S4" t="n">
+        <v>200</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Seppo Ormiskangas</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Seppo Ormiskangas</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 2708-2020 artfynd.xlsx
+++ b/artfynd/A 2708-2020 artfynd.xlsx
@@ -919,7 +919,7 @@
         <v>123404102</v>
       </c>
       <c r="B4" t="n">
-        <v>57497</v>
+        <v>57503</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 2708-2020 artfynd.xlsx
+++ b/artfynd/A 2708-2020 artfynd.xlsx
@@ -919,7 +919,7 @@
         <v>123404102</v>
       </c>
       <c r="B4" t="n">
-        <v>57503</v>
+        <v>57506</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 2708-2020 artfynd.xlsx
+++ b/artfynd/A 2708-2020 artfynd.xlsx
@@ -919,7 +919,7 @@
         <v>123404102</v>
       </c>
       <c r="B4" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
